--- a/output/pdf_financials_xlsx/GOH.xlsx
+++ b/output/pdf_financials_xlsx/GOH.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.9113790000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.199604</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.236734</v>
       </c>
     </row>
     <row r="93">
@@ -3133,7 +3133,11 @@
           <t>Warrant reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3162,7 +3166,11 @@
           <t>Share-based payment reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3443,7 +3451,11 @@
           <t>Warrant reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.555437</v>
       </c>
@@ -3472,7 +3484,11 @@
           <t>Share-based payment reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.355942</v>
       </c>

--- a/output/pdf_financials_xlsx/GOH.xlsx
+++ b/output/pdf_financials_xlsx/GOH.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008255</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003932</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.267754</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008255</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003932</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.267754</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.048116</v>
+        <v>0.039861</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011906</v>
+        <v>0.007974</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.367477</v>
+        <v>0.09972300000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007122</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007122</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4482,7 +4482,11 @@
           <t>Interest accretion on lease payments</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.003467</v>
       </c>
@@ -4606,7 +4610,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>-0.010589</v>
       </c>

--- a/output/pdf_financials_xlsx/GOH.xlsx
+++ b/output/pdf_financials_xlsx/GOH.xlsx
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.09316199999999999</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.016387</v>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.246747</v>
+        <v>0.339909</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.128229</v>
@@ -4548,7 +4548,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.09316199999999999</v>
       </c>
